--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N47_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.50677250751179</v>
+        <v>3.819850532470666</v>
       </c>
       <c r="D2" t="n">
-        <v>24.64563990346273</v>
+        <v>4.004916484312695</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
